--- a/Kachi_Gun/Table/Shop.xlsx
+++ b/Kachi_Gun/Table/Shop.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -653,7 +653,7 @@
     </row>
     <row r="4" ht="19" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
     </row>
     <row r="5" ht="19" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
     </row>
     <row r="6" ht="19" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -1128,6 +1128,54 @@
       <c r="J13" s="5" t="inlineStr">
         <is>
           <t>기획 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>free_gems_ad</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ad_Gems</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>무료 다이아</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>광고 1편 · 다이아 40 · 하루 3번</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>광고</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Gems+40 (Global_Config AdGems_Daily·AdGems_Amount)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>구현 완료 (10-20)</t>
         </is>
       </c>
     </row>

--- a/Kachi_Gun/Table/Shop.xlsx
+++ b/Kachi_Gun/Table/Shop.xlsx
@@ -912,7 +912,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>S 등급 레이저 건 즉시 지급</t>
+          <t>레이저탄_S 즉시 지급</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">

--- a/Kachi_Gun/Table/Shop.xlsx
+++ b/Kachi_Gun/Table/Shop.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -653,11 +653,11 @@
     </row>
     <row r="4" ht="19" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>remove_forced_ads</t>
+          <t>remove_all_ads</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -667,45 +667,43 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>강제 광고 제거</t>
+          <t>모든 광고 제거</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>자동 전면 광고 제거 + 돼지저금통</t>
+          <t>보상형 광고도 바로 보상</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>$1.99</t>
-        </is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>9900</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>NoForcedAds</t>
+          <t>NoAllAds</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>UI 구현</t>
+          <t>UI 구현 · 10-26 원화 가격</t>
         </is>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>remove_all_ads</t>
+        <v>5</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>auto_upgrade</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -715,470 +713,226 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>모든 광고 제거</t>
+          <t>자동강화 패키지</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>보상형 광고도 바로 보상</t>
+          <t>하단 강화 자동 + 다이아 500</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>$9.99</t>
-        </is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>5900</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>NoAllAds</t>
+          <t>AutoUpgrade</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>UI 구현</t>
+          <t>UI 구현 · 10-26 원화 가격</t>
         </is>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>auto_upgrade</t>
+        <v>9</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>gem_pack_small</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>IAP_Pack</t>
+          <t>Gem_Shop</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>자동강화 패키지</t>
+          <t>다이아 한 줌 (500)</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>하단 강화 자동 + 다이아 500</t>
+          <t>다이아 500개 즉시 획득</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>$3.99</t>
-        </is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2900</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>500</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>AutoUpgrade</t>
+          <t>Gems+500</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>UI 구현</t>
+          <t>기획 추가 · 10-26 원화 가격</t>
         </is>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>perma_buff</t>
+          <t>gem_pack_mid</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>IAP_Pack</t>
+          <t>Gem_Shop</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>영구 3배 버프</t>
+          <t>다이아 주머니 (1,800)</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>공격력·돈 x3 영구 + 다이아 1,000</t>
+          <t>다이아 1,800개 즉시 획득</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>$7.99</t>
-        </is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>5900</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>PermaAtkGold3x</t>
+        <v>1800</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Gems+1800</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>UI 구현</t>
+          <t>기획 추가 · 10-26 원화 가격</t>
         </is>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>mine_ticket</t>
+        <v>11</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>gem_pack_large</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>IAP_Pack</t>
+          <t>Gem_Shop</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>광산 티켓 확장</t>
+          <t>다이아 상자 (4,200)</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>하루 광산 티켓 2 → 6 + 다이아 500</t>
+          <t>다이아 4,200개 즉시 획득</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>$3.99</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>DailyMineTickets=6</t>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>11900</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>4200</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Gems+4200</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>UI 구현</t>
+          <t>기획 추가 · 10-26 원화 가격</t>
         </is>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>hotdeal_laser</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>IAP_Pack</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>핫딜 레이저 총알</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>레이저탄_S 즉시 지급</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>$0.99</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>WeaponCode=44 (S 레이저)</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>UI 구현</t>
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>free_gems_ad</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ad_Gems</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>무료 다이아</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>광고 1편 · 다이아 40 · 하루 3번</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>광고</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>40</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Gems+40 (Global_Config AdGems_Daily·AdGems_Amount)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>구현 완료 (10-20)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>gem_pack_small</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Gem_Shop</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>다이아 한 줌 (500)</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>다이아 500개 즉시 획득</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>$1.99</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Gems+500</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>기획 추가</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>gem_pack_mid</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Gem_Shop</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>다이아 주머니 (1,800)</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>다이아 1,800개 즉시 획득</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>$4.99</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>Gems+1800</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>기획 추가</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>gem_pack_large</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Gem_Shop</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>다이아 상자 (4,200)</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>다이아 4,200개 즉시 획득</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>$9.99</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>4200</v>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>Gems+4200</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>기획 추가</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>gold_instant_30m</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Gold_Shop</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>30분 방치 골드 상자</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>현재 스테이지 기준 600마리 처치 골드</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Gems</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>100 다이아</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>StageGold * 600</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>기획 추가</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>free_gems_ad</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ad_Gems</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>무료 다이아</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>광고 1편 · 다이아 40 · 하루 3번</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Ad</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>광고</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>40</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Gems+40 (Global_Config AdGems_Daily·AdGems_Amount)</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>구현 완료 (10-20)</t>
-        </is>
-      </c>
-    </row>
+    <row r="10" ht="19" customHeight="1"/>
+    <row r="11" ht="19" customHeight="1"/>
+    <row r="12" ht="19" customHeight="1"/>
+    <row r="13" ht="19" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
